--- a/artfynd/A 21520-2024 artfynd.xlsx
+++ b/artfynd/A 21520-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117905325</v>
+        <v>117905574</v>
       </c>
       <c r="B2" t="n">
-        <v>94610</v>
+        <v>78125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569190</v>
+        <v>569128</v>
       </c>
       <c r="R2" t="n">
-        <v>6516167</v>
+        <v>6516048</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117905817</v>
+        <v>117904689</v>
       </c>
       <c r="B3" t="n">
-        <v>79098</v>
+        <v>104929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Stormkappan (Stormkappan), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569153</v>
+        <v>569140</v>
       </c>
       <c r="R3" t="n">
-        <v>6516027</v>
+        <v>6515820</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117905461</v>
+        <v>117905325</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>94610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117904689</v>
+        <v>117905461</v>
       </c>
       <c r="B5" t="n">
-        <v>104929</v>
+        <v>79098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormkappan (Stormkappan), Ög</t>
+          <t>Fräkenkärret (Fräkenkärret), Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569140</v>
+        <v>569190</v>
       </c>
       <c r="R5" t="n">
-        <v>6515820</v>
+        <v>6516167</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117905574</v>
+        <v>117905817</v>
       </c>
       <c r="B6" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569128</v>
+        <v>569153</v>
       </c>
       <c r="R6" t="n">
-        <v>6516048</v>
+        <v>6516027</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117975680</v>
+        <v>117975644</v>
       </c>
       <c r="B7" t="n">
-        <v>90893</v>
+        <v>56241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,26 +1205,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>208257</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1232,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569025</v>
+        <v>569107</v>
       </c>
       <c r="R7" t="n">
-        <v>6516058</v>
+        <v>6515790</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,21 +1281,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1310,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117975644</v>
+        <v>117975661</v>
       </c>
       <c r="B8" t="n">
-        <v>56241</v>
+        <v>90499</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,32 +1309,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208257</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569107</v>
+        <v>569157</v>
       </c>
       <c r="R8" t="n">
-        <v>6515790</v>
+        <v>6516067</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117975661</v>
+        <v>117975626</v>
       </c>
       <c r="B9" t="n">
-        <v>90499</v>
+        <v>84372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>241</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569157</v>
+        <v>569070</v>
       </c>
       <c r="R9" t="n">
-        <v>6516067</v>
+        <v>6515901</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117975626</v>
+        <v>117975680</v>
       </c>
       <c r="B10" t="n">
-        <v>84372</v>
+        <v>90893</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>241</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569070</v>
+        <v>569025</v>
       </c>
       <c r="R10" t="n">
-        <v>6515901</v>
+        <v>6516058</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1614,6 +1599,21 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 21520-2024 artfynd.xlsx
+++ b/artfynd/A 21520-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117905574</v>
+        <v>117905325</v>
       </c>
       <c r="B2" t="n">
-        <v>78125</v>
+        <v>94612</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569128</v>
+        <v>569190</v>
       </c>
       <c r="R2" t="n">
-        <v>6516048</v>
+        <v>6516167</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117904689</v>
+        <v>117905461</v>
       </c>
       <c r="B3" t="n">
-        <v>104929</v>
+        <v>79100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormkappan (Stormkappan), Ög</t>
+          <t>Fräkenkärret (Fräkenkärret), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569140</v>
+        <v>569190</v>
       </c>
       <c r="R3" t="n">
-        <v>6515820</v>
+        <v>6516167</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117905325</v>
+        <v>117904689</v>
       </c>
       <c r="B4" t="n">
-        <v>94610</v>
+        <v>104931</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Stormkappan (Stormkappan), Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569190</v>
+        <v>569140</v>
       </c>
       <c r="R4" t="n">
-        <v>6516167</v>
+        <v>6515820</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117905461</v>
+        <v>117905574</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>78127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569190</v>
+        <v>569128</v>
       </c>
       <c r="R5" t="n">
-        <v>6516167</v>
+        <v>6516048</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1090,7 +1090,7 @@
         <v>117905817</v>
       </c>
       <c r="B6" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>117975661</v>
       </c>
       <c r="B8" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117975626</v>
+        <v>117975680</v>
       </c>
       <c r="B9" t="n">
-        <v>84372</v>
+        <v>90895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>241</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569070</v>
+        <v>569025</v>
       </c>
       <c r="R9" t="n">
-        <v>6515901</v>
+        <v>6516058</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,6 +1493,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1509,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117975680</v>
+        <v>117975626</v>
       </c>
       <c r="B10" t="n">
-        <v>90893</v>
+        <v>84374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1536,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>241</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569025</v>
+        <v>569070</v>
       </c>
       <c r="R10" t="n">
-        <v>6516058</v>
+        <v>6515901</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1599,21 +1614,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 21520-2024 artfynd.xlsx
+++ b/artfynd/A 21520-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117905817</v>
+        <v>117975626</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Tummetorp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569153</v>
+        <v>569070</v>
       </c>
       <c r="R2" t="n">
-        <v>6516027</v>
+        <v>6515901</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117905461</v>
+        <v>117905574</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Fräkenkärret, Fräkenkärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569190</v>
+        <v>569128</v>
       </c>
       <c r="R3" t="n">
-        <v>6516167</v>
+        <v>6516048</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,53 +873,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117905325</v>
+        <v>117975661</v>
       </c>
       <c r="B4" t="n">
-        <v>94614</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Tummetorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569190</v>
+        <v>569157</v>
       </c>
       <c r="R4" t="n">
-        <v>6516167</v>
+        <v>6516067</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,68 +955,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117905574</v>
+        <v>117905325</v>
       </c>
       <c r="B5" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fräkenkärret (Fräkenkärret), Ög</t>
+          <t>Fräkenkärret, Fräkenkärret, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569128</v>
+        <v>569190</v>
       </c>
       <c r="R5" t="n">
-        <v>6516048</v>
+        <v>6516167</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117904689</v>
+        <v>117975680</v>
       </c>
       <c r="B6" t="n">
-        <v>104934</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,41 +1082,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormkappan (Stormkappan), Ög</t>
+          <t>Tummetorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569140</v>
+        <v>569025</v>
       </c>
       <c r="R6" t="n">
-        <v>6515820</v>
+        <v>6516058</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1139,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,33 +1153,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117975661</v>
+        <v>117905461</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,40 +1198,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tummetorp, Ög</t>
+          <t>Fräkenkärret, Fräkenkärret, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569157</v>
+        <v>569190</v>
       </c>
       <c r="R7" t="n">
-        <v>6516067</v>
+        <v>6516167</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,34 +1266,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117975626</v>
+        <v>117905817</v>
       </c>
       <c r="B8" t="n">
-        <v>84376</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,40 +1295,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>241</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tummetorp, Ög</t>
+          <t>Fräkenkärret, Fräkenkärret, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569070</v>
+        <v>569153</v>
       </c>
       <c r="R8" t="n">
-        <v>6515901</v>
+        <v>6516027</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,34 +1363,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117975680</v>
+        <v>117975644</v>
       </c>
       <c r="B9" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,26 +1392,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>208257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1444,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569025</v>
+        <v>569107</v>
       </c>
       <c r="R9" t="n">
-        <v>6516058</v>
+        <v>6515790</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,21 +1468,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1522,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117975644</v>
+        <v>117904689</v>
       </c>
       <c r="B10" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,42 +1495,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208257</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tummetorp, Ög</t>
+          <t>Stormkappan, Stormkappan, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569107</v>
+        <v>569140</v>
       </c>
       <c r="R10" t="n">
-        <v>6515790</v>
+        <v>6515820</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,12 +1553,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,19 +1567,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 21520-2024 artfynd.xlsx
+++ b/artfynd/A 21520-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117975626</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117905574</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117975661</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117905325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117975680</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117905461</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117905817</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117975644</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,8 +1627,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117904689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>